--- a/storage/templates/prestamo_general.xlsx
+++ b/storage/templates/prestamo_general.xlsx
@@ -1,21 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sistema_hospital\storage\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F221866F-64C2-4665-B5D2-8082C01EE7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" r:id="rId4"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
   <si>
     <t>Guatemala,</t>
   </si>
@@ -41,9 +59,6 @@
     <t>Servicio de Unidad de Atencion Integral</t>
   </si>
   <si>
-    <t>Justificación del préstamo:</t>
-  </si>
-  <si>
     <t>Se dejan temporalmente bajo responsabilidad de la persona indicada los bienes descritos a continuación, durante el período establecido.</t>
   </si>
   <si>
@@ -141,164 +156,140 @@
   </si>
   <si>
     <t xml:space="preserve">Encargada del  Departamento de Activos Fijos </t>
+  </si>
+  <si>
+    <t>Evelyn Castañeda de Tejada</t>
+  </si>
+  <si>
+    <t>Razón del préstamo:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;Q&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="_-[$Q-100A]* #,##0.00_-;\-[$Q-100A]* #,##0.00_-;_-[$Q-100A]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16">
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+  <fonts count="20" x14ac:knownFonts="1">
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Tahoma"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="20"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -309,7 +300,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -387,255 +378,278 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="164" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="164" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="165" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="12" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="165" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" quotePrefix="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="15" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="15" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" quotePrefix="1" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="80">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -656,7 +670,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Imagen 2" descr=""/>
+        <xdr:cNvPr id="2" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -668,7 +688,8 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm rot="0">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
           <a:ext cx="3352800" cy="885825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -967,47 +988,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:P67"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="11.44140625" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" customWidth="true" style="8"/>
-    <col min="2" max="2" width="13" customWidth="true" style="7"/>
-    <col min="3" max="3" width="29" customWidth="true" style="15"/>
-    <col min="4" max="4" width="10.21875" customWidth="true" style="15"/>
-    <col min="5" max="5" width="15.33203125" customWidth="true" style="9"/>
-    <col min="6" max="6" width="12.5546875" customWidth="true" style="9"/>
+    <col min="1" max="1" width="6.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13" style="7" customWidth="1"/>
+    <col min="3" max="3" width="29" style="15" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="15" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" style="9" customWidth="1"/>
     <col min="7" max="7" width="11.44140625" style="10"/>
     <col min="8" max="8" width="11.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="8"/>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
     </row>
-    <row r="2" spans="1:16" customHeight="1" ht="15.6">
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-    </row>
-    <row r="3" spans="1:16" customHeight="1" ht="16.2">
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
+    <row r="2" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+    </row>
+    <row r="3" spans="1:16" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
       <c r="E3" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="71"/>
-    </row>
-    <row r="4" spans="1:16" customHeight="1" ht="18">
+      <c r="G3" s="49"/>
+    </row>
+    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="11"/>
       <c r="C4" s="33"/>
       <c r="D4" s="33"/>
@@ -1019,12 +1038,12 @@
       </c>
       <c r="G4" s="35"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" s="12"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -1032,50 +1051,50 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:16" customHeight="1" ht="14.4">
-      <c r="A7" s="65" t="s">
+    <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="65"/>
-      <c r="C7" s="75" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="75"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-    </row>
-    <row r="8" spans="1:16" customHeight="1" ht="15">
-      <c r="A8" s="64" t="s">
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+    </row>
+    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="76" t="s">
+      <c r="B8" s="56"/>
+      <c r="C8" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="76"/>
+      <c r="D8" s="55"/>
       <c r="E8" s="8"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-    </row>
-    <row r="9" spans="1:16" customHeight="1" ht="15">
-      <c r="A9" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+    </row>
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="79" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="79"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
     </row>
-    <row r="10" spans="1:16" customHeight="1" ht="15">
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="30"/>
       <c r="B10" s="30"/>
       <c r="C10" s="23"/>
@@ -1086,38 +1105,38 @@
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
     </row>
-    <row r="11" spans="1:16" customHeight="1" ht="33.6">
-      <c r="A11" s="66" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-    </row>
-    <row r="12" spans="1:16" customHeight="1" ht="15">
-      <c r="D12" s="45"/>
+    <row r="11" spans="1:16" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+    </row>
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D12" s="41"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="74"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
-    </row>
-    <row r="13" spans="1:16" customHeight="1" ht="15">
-      <c r="A13" s="67" t="s">
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="52"/>
+      <c r="P12" s="52"/>
+    </row>
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="58"/>
+      <c r="C13" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="67"/>
-      <c r="C13" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="44"/>
+      <c r="E13" s="40"/>
       <c r="G13" s="9"/>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
@@ -1126,11 +1145,11 @@
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
     </row>
-    <row r="14" spans="1:16" customHeight="1" ht="15">
+    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
@@ -1141,435 +1160,438 @@
       <c r="O14" s="17"/>
       <c r="P14" s="17"/>
     </row>
-    <row r="15" spans="1:16" customHeight="1" ht="27" s="22" customFormat="1">
-      <c r="A15" s="46" t="s">
+    <row r="15" spans="1:16" s="22" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="68" t="s">
+      <c r="C15" s="60"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="20" t="s">
+      <c r="F15" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="G15" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="21" t="s">
+    </row>
+    <row r="16" spans="1:16" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="66">
+        <v>1</v>
+      </c>
+      <c r="B16" s="67" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A16" s="37">
+      <c r="C16" s="68"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="71"/>
+      <c r="G16" s="72">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="66">
         <v>1</v>
       </c>
-      <c r="B16" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="38" t="s">
+      <c r="B17" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40">
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A17" s="37">
+      <c r="C17" s="68"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="71"/>
+      <c r="G17" s="72">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="66">
         <v>1</v>
       </c>
-      <c r="B17" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="38" t="s">
+      <c r="B18" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="68"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40">
+      <c r="F18" s="71"/>
+      <c r="G18" s="72">
         <v>2380</v>
       </c>
     </row>
-    <row r="18" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A18" s="37">
+    <row r="19" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="66">
         <v>1</v>
       </c>
-      <c r="B18" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="38" t="s">
+      <c r="B19" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="68"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40">
+      <c r="F19" s="71"/>
+      <c r="G19" s="72">
         <v>2380</v>
       </c>
     </row>
-    <row r="19" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A19" s="37">
+    <row r="20" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="66">
         <v>1</v>
       </c>
-      <c r="B19" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="38" t="s">
+      <c r="B20" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40">
-        <v>2380</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A20" s="37">
+      <c r="C20" s="68"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="71"/>
+      <c r="G20" s="72">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="66">
         <v>1</v>
       </c>
-      <c r="B20" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="38" t="s">
+      <c r="B21" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="68"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40">
+      <c r="F21" s="71"/>
+      <c r="G21" s="72">
         <v>1550</v>
       </c>
     </row>
-    <row r="21" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A21" s="37">
+    <row r="22" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="66">
         <v>1</v>
       </c>
-      <c r="B21" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="38" t="s">
+      <c r="B22" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="68"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40">
+      <c r="F22" s="71"/>
+      <c r="G22" s="72">
         <v>1550</v>
       </c>
     </row>
-    <row r="22" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A22" s="37">
+    <row r="23" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="66">
         <v>1</v>
       </c>
-      <c r="B22" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="38" t="s">
+      <c r="B23" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="68"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40">
+      <c r="F23" s="71"/>
+      <c r="G23" s="72">
         <v>1550</v>
       </c>
     </row>
-    <row r="23" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A23" s="37">
+    <row r="24" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="66">
         <v>1</v>
       </c>
-      <c r="B23" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="38" t="s">
+      <c r="B24" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="68"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40">
+      <c r="F24" s="71"/>
+      <c r="G24" s="72">
         <v>1550</v>
       </c>
     </row>
-    <row r="24" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A24" s="37">
+    <row r="25" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="66">
         <v>1</v>
       </c>
-      <c r="B24" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="60"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="38" t="s">
+      <c r="B25" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="68"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40">
+      <c r="F25" s="71"/>
+      <c r="G25" s="72">
         <v>1550</v>
       </c>
     </row>
-    <row r="25" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A25" s="37">
+    <row r="26" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="66">
         <v>1</v>
       </c>
-      <c r="B25" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="38" t="s">
+      <c r="B26" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40">
+      <c r="F26" s="71"/>
+      <c r="G26" s="72">
         <v>1550</v>
       </c>
     </row>
-    <row r="26" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A26" s="37">
+    <row r="27" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="66">
         <v>1</v>
       </c>
-      <c r="B26" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="38" t="s">
+      <c r="B27" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="68"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40">
+      <c r="F27" s="71"/>
+      <c r="G27" s="72">
         <v>1550</v>
       </c>
     </row>
-    <row r="27" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A27" s="37">
+    <row r="28" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="66">
         <v>1</v>
       </c>
-      <c r="B27" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="60"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="38" t="s">
+      <c r="B28" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="68"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40">
+      <c r="F28" s="71"/>
+      <c r="G28" s="72">
         <v>1550</v>
       </c>
     </row>
-    <row r="28" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A28" s="37">
+    <row r="29" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="66">
         <v>1</v>
       </c>
-      <c r="B28" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="60"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="38" t="s">
+      <c r="B29" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="68"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40">
+      <c r="F29" s="71"/>
+      <c r="G29" s="72">
         <v>1550</v>
       </c>
     </row>
-    <row r="29" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A29" s="37">
+    <row r="30" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="66">
         <v>1</v>
       </c>
-      <c r="B29" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="38" t="s">
+      <c r="B30" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="68"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40">
+      <c r="F30" s="71"/>
+      <c r="G30" s="72">
         <v>1550</v>
       </c>
     </row>
-    <row r="30" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A30" s="37">
+    <row r="31" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="66">
         <v>1</v>
       </c>
-      <c r="B30" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="38" t="s">
+      <c r="B31" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40">
-        <v>1550</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A31" s="37">
+      <c r="C31" s="68"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="70" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" s="71"/>
+      <c r="G31" s="72">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="22" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="66">
         <v>1</v>
       </c>
-      <c r="B31" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="60"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="38" t="s">
+      <c r="B32" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="68"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40">
+      <c r="F32" s="71"/>
+      <c r="G32" s="72">
         <v>1420</v>
       </c>
     </row>
-    <row r="32" spans="1:16" customHeight="1" ht="15.6" s="22" customFormat="1">
-      <c r="A32" s="37">
-        <v>1</v>
-      </c>
-      <c r="B32" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="60"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="38" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="73"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="74"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="A33" s="7"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" s="48">
+      <c r="G33" s="76">
         <f>SUM(G16:G32)</f>
         <v>28655</v>
       </c>
     </row>
-    <row r="34" spans="1:16" customHeight="1" ht="14.4">
+    <row r="34" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:16" customHeight="1" ht="15">
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="36"/>
       <c r="D35" s="36"/>
-      <c r="G35" s="41"/>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="56" t="s">
+      <c r="G35" s="37"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="63" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="63"/>
+      <c r="D36" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="B36" s="56"/>
-      <c r="D36" s="14" t="s">
-        <v>40</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:16" customHeight="1" ht="15.6">
-      <c r="A37" s="53"/>
-      <c r="E37" s="52"/>
+    <row r="37" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="46"/>
+      <c r="E37" s="45"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:16" customHeight="1" ht="18.75">
+    <row r="38" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="32"/>
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="57"/>
+      <c r="C38" s="64"/>
       <c r="D38" s="30"/>
-      <c r="E38" s="62" t="s">
+      <c r="E38" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="62"/>
-      <c r="G38" s="62"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:16">
-      <c r="B39" s="58" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B39" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="58"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="63"/>
-    </row>
-    <row r="40" spans="1:16" customHeight="1" ht="15">
+      <c r="C39" s="65"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
     </row>
-    <row r="41" spans="1:16" customHeight="1" ht="15">
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D41" s="6"/>
       <c r="E41" s="5"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
     </row>
-    <row r="42" spans="1:16" customHeight="1" ht="15">
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="6"/>
     </row>
-    <row r="43" spans="1:16" customHeight="1" ht="15">
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F43" s="16"/>
       <c r="G43" s="16"/>
       <c r="H43" s="16"/>
     </row>
-    <row r="44" spans="1:16" customHeight="1" ht="15">
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F44" s="16"/>
       <c r="G44" s="16"/>
       <c r="H44" s="16"/>
     </row>
-    <row r="45" spans="1:16" customHeight="1" ht="15.6">
-      <c r="B45" s="72"/>
-      <c r="C45" s="72"/>
-      <c r="D45" s="72"/>
-      <c r="E45" s="72"/>
-      <c r="F45" s="72"/>
+    <row r="45" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="50"/>
+      <c r="C45" s="50"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
       <c r="G45" s="25"/>
       <c r="H45" s="16"/>
     </row>
-    <row r="46" spans="1:16" customHeight="1" ht="15">
-      <c r="B46" s="73"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="73"/>
+    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="51"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
       <c r="G46" s="16"/>
       <c r="H46" s="16"/>
       <c r="I46" s="26"/>
       <c r="J46" s="26"/>
     </row>
-    <row r="47" spans="1:16" customHeight="1" ht="9" hidden="true">
+    <row r="47" spans="1:10" ht="9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
       <c r="F47" s="16"/>
       <c r="G47" s="16"/>
     </row>
-    <row r="48" spans="1:16" customHeight="1" ht="9">
+    <row r="48" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
@@ -1577,7 +1599,7 @@
       <c r="F48" s="17"/>
       <c r="G48" s="17"/>
     </row>
-    <row r="49" spans="1:16" customHeight="1" ht="9">
+    <row r="49" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
@@ -1585,7 +1607,7 @@
       <c r="F49" s="17"/>
       <c r="G49" s="17"/>
     </row>
-    <row r="50" spans="1:16" customHeight="1" ht="9">
+    <row r="50" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -1593,7 +1615,7 @@
       <c r="F50" s="17"/>
       <c r="G50" s="17"/>
     </row>
-    <row r="51" spans="1:16" customHeight="1" ht="9">
+    <row r="51" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -1601,7 +1623,7 @@
       <c r="F51" s="17"/>
       <c r="G51" s="17"/>
     </row>
-    <row r="52" spans="1:16" customHeight="1" ht="9">
+    <row r="52" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -1609,7 +1631,7 @@
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
     </row>
-    <row r="53" spans="1:16" customHeight="1" ht="9">
+    <row r="53" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
       <c r="D53" s="17"/>
@@ -1617,7 +1639,7 @@
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
     </row>
-    <row r="54" spans="1:16" customHeight="1" ht="9">
+    <row r="54" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
@@ -1625,7 +1647,7 @@
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
     </row>
-    <row r="55" spans="1:16" customHeight="1" ht="9">
+    <row r="55" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
@@ -1633,54 +1655,75 @@
       <c r="F55" s="17"/>
       <c r="G55" s="17"/>
     </row>
-    <row r="60" spans="1:16" customHeight="1" ht="20.25">
+    <row r="60" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
     </row>
-    <row r="62" spans="1:16" customHeight="1" ht="15.75">
+    <row r="62" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
       <c r="G62" s="19"/>
       <c r="H62" s="17"/>
     </row>
-    <row r="63" spans="1:16" customHeight="1" ht="15.75">
+    <row r="63" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
       <c r="G63" s="19"/>
       <c r="H63" s="17"/>
     </row>
-    <row r="64" spans="1:16" customHeight="1" ht="24.75">
+    <row r="64" spans="2:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
       <c r="G64" s="27"/>
     </row>
-    <row r="65" spans="1:16" customHeight="1" ht="26.25">
+    <row r="65" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="24"/>
       <c r="G65" s="27"/>
     </row>
-    <row r="66" spans="1:16" customHeight="1" ht="15">
+    <row r="66" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="24"/>
       <c r="F66" s="18"/>
       <c r="G66" s="28"/>
       <c r="H66" s="16"/>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="E67" s="18"/>
       <c r="F67" s="18"/>
       <c r="G67" s="19"/>
       <c r="H67" s="29"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="37">
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B46:F46"/>
@@ -1697,30 +1740,9 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E38:G39"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="5" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
+  <pageSetup paperSize="5" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>